--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3557-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3557-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C081B4F0-88C0-47AE-BA9F-525557E73EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33221EB5-C899-48B8-BF8D-4D7EB481F9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{47703D3F-4E40-4B77-9780-7CED3A6D5695}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F93CF33E-2B26-453B-AAE4-13A4068CF9BC}"/>
   </bookViews>
   <sheets>
     <sheet name="3557-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1475,23 +1475,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6A125A-0A55-4A4B-B074-49F9AF370DFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88337D39-8A6E-4113-9B83-02E0149918A3}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1645,7 +1645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>2024</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>2023</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="40">
         <v>2022</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>26</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="38">
         <v>2021</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>2020</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>26</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>26</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>26</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>26</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="38">
         <v>2019</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>2018</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2017</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2016</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>2015</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>2014</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2013</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2012</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2011</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2010</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2009</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2008</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
         <v>43</v>
       </c>
